--- a/data/trans_camb/P43B-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P43B-Habitat-trans_camb.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,22</t>
+          <t>2,09</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,22</t>
+          <t>2,09</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 5,01</t>
+          <t>-3,55; 5,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 6,38</t>
+          <t>-2,37; 6,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 5,01</t>
+          <t>-3,55; 5,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 6,38</t>
+          <t>-2,37; 6,34</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -657,22 +657,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,59; 94,09</t>
+          <t>-36,37; 110,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,09; 120,76</t>
+          <t>-23,52; 116,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-43,59; 94,09</t>
+          <t>-36,37; 110,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,09; 120,76</t>
+          <t>-23,52; 116,1</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>2,76</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>2,76</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 3,35</t>
+          <t>-5,03; 3,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 6,59</t>
+          <t>-1,43; 7,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 3,35</t>
+          <t>-5,03; 3,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 6,59</t>
+          <t>-1,43; 7,0</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -773,22 +773,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-36,91; 37,56</t>
+          <t>-36,66; 36,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,59; 72,12</t>
+          <t>-9,85; 74,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-36,91; 37,56</t>
+          <t>-36,66; 36,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,59; 72,12</t>
+          <t>-9,85; 74,77</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-6,94</t>
+          <t>4,48</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-6,94</t>
+          <t>4,48</t>
         </is>
       </c>
     </row>
@@ -833,22 +833,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,38; -3,35</t>
+          <t>-15,1; -3,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 4,39</t>
+          <t>-1,64; 10,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,38; -3,35</t>
+          <t>-15,1; -3,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 4,39</t>
+          <t>-1,64; 10,39</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-35,49%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-35,49%</t>
+          <t>22,92%</t>
         </is>
       </c>
     </row>
@@ -889,22 +889,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-66,22; -19,42</t>
+          <t>-65,43; -22,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-76,79; 24,16</t>
+          <t>-7,09; 67,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-66,22; -19,42</t>
+          <t>-65,43; -22,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-76,79; 24,16</t>
+          <t>-7,09; 67,42</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>6,3</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>6,3</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 5,21</t>
+          <t>-5,09; 5,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,66; 11,53</t>
+          <t>1,47; 11,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 5,21</t>
+          <t>-5,09; 5,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,66; 11,53</t>
+          <t>1,47; 11,01</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,3%</t>
         </is>
       </c>
     </row>
@@ -1005,22 +1005,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,94; 34,75</t>
+          <t>-25,34; 33,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,54; 77,59</t>
+          <t>6,55; 76,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-24,94; 34,75</t>
+          <t>-25,34; 33,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,54; 77,59</t>
+          <t>6,55; 76,54</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>4,14</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>4,14</t>
         </is>
       </c>
     </row>
@@ -1065,22 +1065,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 0,6</t>
+          <t>-4,43; 0,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 4,47</t>
+          <t>1,33; 6,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 0,6</t>
+          <t>-4,43; 0,5</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 4,47</t>
+          <t>1,33; 6,55</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -1121,22 +1121,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-29,46; 4,37</t>
+          <t>-27,64; 4,05</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-28,39; 32,78</t>
+          <t>8,11; 50,54</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-29,46; 4,37</t>
+          <t>-27,64; 4,05</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-28,39; 32,78</t>
+          <t>8,11; 50,54</t>
         </is>
       </c>
     </row>
